--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>45</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>25/07 16:45</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>27/07 13:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>25/07 19:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>24/07 18:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F18" t="n">
+        <v>2.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>23/07 02:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>24/07 01:20</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F21" t="n">
+        <v>2.75</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>23/07 09:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F22" t="n">
+        <v>2.45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>24/07 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
+      <c r="F23" t="n">
+        <v>1.28</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>23/07 19:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="F24" t="n">
+        <v>1.17</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,187 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45861.08248072744</v>
+        <v>45861.08248072916</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico N</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atletico Nacional – Santa FePrimera A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>26/07 01:30</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+42,5%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45861.15523750979</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Shanghai S</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua – Henan Songshan LongmenSuper League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>27/07 11:35</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+5,52%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45861.15523750979</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Deportes T</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Deportes Tolima – Deportivo PereiraPrimera A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>25/07 23:20</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+2,78%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45861.15523750979</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Jeju Unite</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jeju United FC – FC SéoulK League 1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>23/07 10:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+0,71%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45861.15523750979</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,10 +1494,8 @@
           <t>26/07 01:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>60</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1510,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45861.15523750979</v>
+        <v>45861.15523751157</v>
       </c>
     </row>
     <row r="26">
@@ -1539,10 +1537,8 @@
           <t>27/07 11:35</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1555,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45861.15523750979</v>
+        <v>45861.15523751157</v>
       </c>
     </row>
     <row r="27">
@@ -1584,10 +1580,8 @@
           <t>25/07 23:20</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>40</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1600,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45861.15523750979</v>
+        <v>45861.15523751157</v>
       </c>
     </row>
     <row r="28">
@@ -1629,10 +1623,8 @@
           <t>23/07 10:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>40</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1645,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45861.15523750979</v>
+        <v>45861.15523751157</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | H 2 (−2.5) | Paide Linn</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Paide Linnameeskond – AIK StockholmEurope - Ligue  Conférence</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>24/07 15:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+0,93%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45861.19665038315</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>24/07 15:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
+      <c r="F29" t="n">
+        <v>3.05</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,142 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45861.19665038315</v>
+        <v>45861.19665038194</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 8.5 - tir cadré | Juventude </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Juventude RS – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24/07 22:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>49,5%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+6,51%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45861.2296693744</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Midtjyl</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FC Midtjylland – HibernianLigue Europa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24/07 17:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+5,95%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45861.2296693744</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Monterrey </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Monterrey – Atlas FCLiga MX - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>27/07 01:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+1,14%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45861.2296693744</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>24/07 22:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F30" t="n">
+        <v>2.15</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45861.2296693744</v>
+        <v>45861.229669375</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>45</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45861.2296693744</v>
+        <v>45861.229669375</v>
       </c>
     </row>
     <row r="32">
@@ -1799,10 +1795,8 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>40</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1815,7 +1809,277 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45861.2296693744</v>
+        <v>45861.229669375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | Van De Zan</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Van De Zandsch – F.MisolicATP - Kitzbuhel</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>23/07 10:10</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+54,7%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45861.27482102712</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | T.Valentov</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>T.Valentova – R.SramkovaWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>23/07 09:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+26,7%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45861.27482102712</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Once Calda</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Once Caldas – San Antonio Bulo BuloInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45861.27482102712</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | J.Ponchet </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>J.Ponchet – B.PalicovaWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>23/07 09:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>78,6%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+2,14%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45861.27482102712</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | L.Jeanjean</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>L.Jeanjean – A.LiWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>23/07 10:10</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+1,65%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45861.27482102712</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | X - aces | D.Salkova </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D.Salkova – K.SiniakovaWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23/07 10:10</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+1,20%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45861.27482102712</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>23/07 10:10</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45861.27482102712</v>
+        <v>45861.27482103009</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>23/07 09:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45861.27482102712</v>
+        <v>45861.27482103009</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.95</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45861.27482102712</v>
+        <v>45861.27482103009</v>
       </c>
     </row>
     <row r="36">
@@ -1973,10 +1967,8 @@
           <t>23/07 09:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="F36" t="n">
+        <v>1.3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1989,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45861.27482102712</v>
+        <v>45861.27482103009</v>
       </c>
     </row>
     <row r="37">
@@ -2018,10 +2010,8 @@
           <t>23/07 10:10</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F37" t="n">
+        <v>1.25</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2034,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45861.27482102712</v>
+        <v>45861.27482103009</v>
       </c>
     </row>
     <row r="38">
@@ -2063,10 +2053,8 @@
           <t>23/07 10:10</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2079,7 +2067,97 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45861.27482102712</v>
+        <v>45861.27482103009</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico M</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – Atlético BucaramangaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>25/07 00:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+38,9%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45861.30991717347</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Shelbourne</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Shelbourne FC – Qarabag FKLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>23/07 18:45</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+2,11%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45861.30991717347</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>25/07 00:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>60</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45861.30991717347</v>
+        <v>45861.30991717592</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>23/07 18:45</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>45</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,412 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45861.30991717347</v>
+        <v>45861.30991717592</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | M.Linette </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M.Linette – A.KalinskayaWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23/07 15:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+32,6%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Yannick Ha</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Yannick Hanfmann – Sebastian BaezATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23/07 09:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>31,0%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+24,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Alexander </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Alexander Shevchenko – Marton Fucsovics385076e7 ATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/07 11:20</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+23,1%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 14.5 - tirs2e équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Corinthians – CruzeiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>23/07 22:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+21,8%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Fluminense</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fluminense – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23/07 22:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>36,3%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | N.Basilash</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>N.Basilashvili – D.PrizmicATP - Umag</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>23/07 16:50</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>68,5%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+9,56%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Bragantino</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bragantino – FlamengoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+9,15%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | R.Bautista</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>R.Bautista – T.Seyboth WildATP - Kitzbuhel</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>23/07 12:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+9,06%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45861.35638500113</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Banfiel</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CA Banfield – Barracas CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>28/07 23:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+8,49%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45861.35638500113</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>23/07 15:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F41" t="n">
+        <v>1.55</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>23/07 09:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>23/07 11:20</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>23/07 22:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F44" t="n">
+        <v>3.2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="45">
@@ -2362,10 +2354,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F45" t="n">
+        <v>3.1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2378,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="46">
@@ -2407,10 +2397,8 @@
           <t>23/07 16:50</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2423,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="47">
@@ -2452,10 +2440,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.8</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2468,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="48">
@@ -2497,10 +2483,8 @@
           <t>23/07 12:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2513,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
       </c>
     </row>
     <row r="49">
@@ -2542,10 +2526,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>50</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2558,7 +2540,187 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45861.35638500113</v>
+        <v>45861.356385</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Francisco </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Francisco Comesana – Arthur CazauxATP - Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>23/07 11:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52,8%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45861.39621718535</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Union Sant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Union Santa Fe – CA TigreLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>26/07 00:15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+11,5%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45861.39621718535</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Damir Dzum</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Damir Dzumhur – Stan WawrinkaATP - Umag</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>23/07 19:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45861.39621718535</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 21.5 - tirs1re équipe | Once Calda</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Once Caldas – San Antonio Bulo BuloInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 21.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>36,1%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+8,25%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45861.39621718535</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>23/07 11:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.25</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45861.39621718535</v>
+        <v>45861.3962171875</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>55</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45861.39621718535</v>
+        <v>45861.3962171875</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>23/07 19:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>10</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45861.39621718535</v>
+        <v>45861.3962171875</v>
       </c>
     </row>
     <row r="53">
@@ -2704,23 +2698,111 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>36,1%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+8,25%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45861.3962171875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 7.5 - tir cadré1re équipe | Gremio RS </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Gremio RS – Alianza LimaInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>+8,25%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>45861.39621718535</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45861.43506130166</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Ceara SC –</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ceara SC – Mirassol FC SPSérie A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>23/07 22:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+11,4%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45861.43506130166</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45861.43506130166</v>
+        <v>45861.4350612963</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>50</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,52 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45861.43506130166</v>
+        <v>45861.4350612963</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Atlanta Dr</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Atlanta Dream – Phoenix MercuryUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>24/07 02:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45861.473029567</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>24/07 02:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>25</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,142 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45861.473029567</v>
+        <v>45861.47302957176</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Zachary Sv</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Zachary Svajda – Jiri LeheckaATP - Washington</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>23/07 15:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+26,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45861.53524114522</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Yibing Wu </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Yibing Wu – Alexei PopyrinATP - Washington</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>23/07 15:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+25,6%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45861.53524114522</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 20.5 - tirs1re équipe | Once Calda</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Once Caldas – San Antonio Bulo BuloInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 20.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+11,2%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45861.53524114522</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>23/07 15:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45861.53524114522</v>
+        <v>45861.53524114583</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>23/07 15:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45861.53524114522</v>
+        <v>45861.53524114583</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,52 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45861.53524114522</v>
+        <v>45861.53524114583</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 7.5 - tir cadré1re équipe | Palestino </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Palestino – BolivarInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>23/07 22:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45861.56987653244</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -2999,10 +2999,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45861.56987653244</v>
+        <v>45861.56987652778</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3016,6 +3016,96 @@
         <v>45861.56987652778</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Fluminense</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fluminense – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>23/07 22:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+8,90%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45861.64393429744</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Vitoria BA – Sport RecifeBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+6,28%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45861.64393429744</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -3042,10 +3042,8 @@
           <t>23/07 22:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.7</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45861.64393429744</v>
+        <v>45861.64393429398</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F62" t="n">
+        <v>2.85</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45861.64393429744</v>
+        <v>45861.64393429398</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3102,6 +3102,141 @@
         <v>45861.64393429398</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | J.Ponchet </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>J.Ponchet – T.ValentovaWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>24/07 08:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+49,6%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45861.72496710832</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | M.Bouzkova</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>M.Bouzkova – A.LiWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>24/07 08:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+39,1%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45861.72496710832</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>25/07 21:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+9,44%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45861.72496710832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -3128,10 +3128,8 @@
           <t>24/07 08:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>6</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45861.72496710832</v>
+        <v>45861.72496710648</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>24/07 08:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45861.72496710832</v>
+        <v>45861.72496710648</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>25/07 21:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>40</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45861.72496710832</v>
+        <v>45861.72496710648</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3231,6 +3231,51 @@
         <v>45861.72496710648</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | NK Celje –</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NK Celje – NK RadomljeSlovénie - Slovénie 1. SNL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>27/07 18:15</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+5,32%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45861.85242623901</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>27/07 18:15</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>35</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,52 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45861.85242623901</v>
+        <v>45861.85242623842</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | SV Ried – </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SV Ried – RB SalzbourgBundesliga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02/08 17:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+4,98%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45861.89105075716</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>50</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,52 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45861.89105075716</v>
+        <v>45861.89105075232</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Once Calda</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Once Caldas – Atletico JuniorPrimera A</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>26/07 23:10</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45861.9327040319</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-23.xlsx
+++ b/data/valuebets_database_2025-07-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,23 +3343,111 @@
           <t>26/07 23:10</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="n">
+        <v>45</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45861.93270402778</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | M.Bouzkova</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>M.Bouzkova – A.LiWTA - Prague F</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>24/07 10:10</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+22,0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45861.97480684645</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Gimnasia L</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata – CA IndependienteLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>27/07 19:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>+11,6%</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>45861.9327040319</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+4,85%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45861.97480684645</v>
       </c>
     </row>
   </sheetData>
